--- a/datatables/datas/游戏副本定义表.xlsx
+++ b/datatables/datas/游戏副本定义表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17230"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="游戏副本定义表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="53">
   <si>
     <t>##var</t>
   </si>
@@ -38,7 +38,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>owning_module</t>
+    <t>game_module</t>
   </si>
   <si>
     <t>identify_type</t>
@@ -74,7 +74,7 @@
     <t>副本名称</t>
   </si>
   <si>
-    <t>所属模块</t>
+    <t>所属游戏模块</t>
   </si>
   <si>
     <t>识别类型</t>
@@ -98,10 +98,46 @@
     <t>祖安废墟</t>
   </si>
   <si>
+    <t>公会副本/祖安废墟/上层</t>
+  </si>
+  <si>
+    <t>祖安废墟（上层）</t>
+  </si>
+  <si>
+    <t>公会副本/祖安废墟/中层</t>
+  </si>
+  <si>
+    <t>祖安废墟（中层）</t>
+  </si>
+  <si>
+    <t>公会副本/祖安废墟/下层</t>
+  </si>
+  <si>
+    <t>祖安废墟（下层）</t>
+  </si>
+  <si>
     <t>公会副本/火焰之心</t>
   </si>
   <si>
     <t>火焰之心</t>
+  </si>
+  <si>
+    <t>公会副本/火焰之心/上层</t>
+  </si>
+  <si>
+    <t>火焰之心（上层）</t>
+  </si>
+  <si>
+    <t>公会副本/火焰之心/中层</t>
+  </si>
+  <si>
+    <t>火焰之心（中层）</t>
+  </si>
+  <si>
+    <t>公会副本/火焰之心/下层</t>
+  </si>
+  <si>
+    <t>火焰之心（下层）</t>
   </si>
   <si>
     <t>公会副本/祭坛外围</t>
@@ -1362,7 +1398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1373,7 +1409,7 @@
     <col min="7" max="7" width="22.5181818181818" style="3" customWidth="1"/>
     <col min="8" max="16357" width="9.13636363636364" style="3" customWidth="1"/>
     <col min="16358" max="16358" width="9.13636363636364" style="3"/>
-    <col min="16359" max="16384" width="9" style="3"/>
+    <col min="16359" max="16383" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
@@ -1564,7 +1600,7 @@
     <row r="10" spans="1:7">
       <c r="A10" s="6"/>
       <c r="B10" s="7">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>31</v>
@@ -1585,7 +1621,7 @@
     <row r="11" spans="1:7">
       <c r="A11" s="6"/>
       <c r="B11" s="7">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>33</v>
@@ -1606,7 +1642,7 @@
     <row r="12" spans="1:7">
       <c r="A12" s="6"/>
       <c r="B12" s="7">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>35</v>
@@ -1627,7 +1663,7 @@
     <row r="13" spans="1:7">
       <c r="A13" s="6"/>
       <c r="B13" s="7">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>37</v>
@@ -1648,7 +1684,7 @@
     <row r="14" spans="1:7">
       <c r="A14" s="6"/>
       <c r="B14" s="7">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>39</v>
@@ -1667,57 +1703,165 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="7">
+        <v>1008</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="8"/>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7">
+        <v>1009</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7">
+        <v>1010</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7">
+        <v>1011</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7">
+        <v>1012</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7">
+        <v>1013</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="8"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:7">
       <c r="A22" s="8"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:7">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:7">
       <c r="A24" s="8"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:7">
       <c r="A25" s="8"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:7">
       <c r="A26" s="8"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:7">
       <c r="A27" s="8"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:7">
       <c r="A28" s="8"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:7">
       <c r="A29" s="8"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:7">
       <c r="A30" s="8"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:7">
       <c r="A31" s="8"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:7">
       <c r="A32" s="8"/>
     </row>
     <row r="33" spans="1:1">
@@ -1835,10 +1979,28 @@
       <c r="A70" s="8"/>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="9"/>
+      <c r="A71" s="8"/>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="9"/>
+      <c r="A72" s="8"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="8"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="8"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="8"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="8"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="9"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
